--- a/docs/SparshaGuard_parameter_sources.xlsx
+++ b/docs/SparshaGuard_parameter_sources.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Still Estimated" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Values from Papers'!$A$4:$L$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sources'!$A$3:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Values from Papers'!$A$4:$L$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sources'!$A$3:$L$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Model v0.3 Params'!$A$3:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE7F6"/>
       </patternFill>
     </fill>
@@ -129,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,10 +168,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -771,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L133"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7867,10 +7875,2002 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>V130</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Body voltage, worst case (incl. walking)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ±20</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>22 °C, 5 % RH</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="H134" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G134,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>Upper end of the body-voltage sweep</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>V131</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Body capacitance to ground on concrete vs wood-frame floor</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>120 vs 60</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Same person; concrete gives about half the voltage</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="H135" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G135,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>Floors change voltage ~2x</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>V132</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Spread of body voltage from capacitance differences alone</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>±30</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="H136" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G136,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr"/>
+      <c r="L136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>V133</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Time for body charge to fall to 100 V without ESD shoes/floor</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>1 – 30</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>With ESD shoes/floor: 0.5–6 s</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="H137" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G137,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>Supports R up to 1e11 Ω (τ up to ~25 s)</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>V134</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>Body capacitance standing on both feet / on one foot</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>160 / 100</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>Vinyl tile</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="H138" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G138,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>Summary article</t>
+        </is>
+      </c>
+      <c r="J138" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>C_B × 0.625 in single support</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>V135</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Body resistance to ground on vinyl tile</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>≈ 10^11</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Ω</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="H139" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G139,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>Summary article</t>
+        </is>
+      </c>
+      <c r="J139" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>Upper end of R range</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>V136</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Lifting a foot raises body voltage</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>8 – 12</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>Walking on resistive floors</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="H140" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G140,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr"/>
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>V137</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Change of body capacitance, sitting on a wooden chair vs standing</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>&lt; 10</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="H141" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G141,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J141" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>Her own movement changes C_B by 2–7 %</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>V138</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>Measured human body capacitance, range</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>50 – 500</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="H142" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G142,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr"/>
+      <c r="L142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>V139</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Body capacitance barefoot on 1 rubber carpet / on 4 carpets</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>295 / 116</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="H143" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G143,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>Snippet</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr"/>
+      <c r="L143" s="6" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>V140</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Static charge</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>Human-body model (test standard)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>150 pF, 330 Ω</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>Discharge time constant ≈ 50 ns; rise time 0.8 ns ±25 %</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>S54</t>
+        </is>
+      </c>
+      <c r="H144" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G144,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J144" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>Charge sharing at contact settles far inside one 2 ms sample</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>V141</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Gait</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Walking cadence, women (normal lab walking)</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>96 – 138</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>steps/min</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>Across the lifespan</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="H145" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G145,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J145" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>1.6–2.3 steps/s</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>V142</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Gait</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>Gait phases: double support / loading response / toe-off</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>0–10 % and 50–60 % / 0–10 % / 60 %</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>% of stride</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>Normal walking</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>S46</t>
+        </is>
+      </c>
+      <c r="H146" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G146,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>Textbook</t>
+        </is>
+      </c>
+      <c r="J146" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>Timing of C_B changes per step</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>V143</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Wrist acceleration (ENMO), slow / normal / brisk walking</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>140 / 210 / 350</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>Adults 40–69, wrist, averaged</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>S43</t>
+        </is>
+      </c>
+      <c r="H147" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G147,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J147" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>Arm-swing amplitude π × ENMO</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>Averaged, not peaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>V144</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Walking periodicity; wrist shows half the step rate</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>≈ 1.7</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>Pooled datasets</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+      <c r="H148" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G148,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>Snippet</t>
+        </is>
+      </c>
+      <c r="J148" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>Arm swing at half the cadence</t>
+        </is>
+      </c>
+      <c r="L148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>V145</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Bus acceleration from standstill / braking into a stop, maxima</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>3.37 / −3.12</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>12 days, sensor on a vertical bar</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+      <c r="H149" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G149,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J149" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>Bus jolts 0.1–0.34 g</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>V146</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>Tram acceleration / braking maxima</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>1.80 / −2.31</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>Same study</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+      <c r="H150" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G150,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr"/>
+      <c r="L150" s="6" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>V147</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Standing-passenger perturbation pulses tested</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>1.5 and 3.0 (acc.), 1.0 and 2.5 (braking)</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Sled tests, 24 volunteers</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>S47</t>
+        </is>
+      </c>
+      <c r="H151" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G151,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr"/>
+      <c r="L151" s="6" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>V148</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>Aggressive-movement classification, smartwatch</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>99.6 % accuracy, 98.4 % sensitivity</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>30 people, scripted punch/shove/slap</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>S34</t>
+        </is>
+      </c>
+      <c r="H152" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G152,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="inlineStr">
+        <is>
+          <t>Benchmark only</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr"/>
+      <c r="L152" s="6" t="inlineStr">
+        <is>
+          <t>Scripted</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>V149</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Fall-sensor false alarms in long-term use</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>0.049 (0.025 improved)</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>per hour</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>16 older adults, 15,500 h</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="H153" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G153,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>Benchmark only</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>Benchmark for unwanted prompts</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>V150</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>Fall-detector false alarms, real-world</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>0 – 0.3</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>per hour</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>≈ 400 h, waist/sternum</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>S56</t>
+        </is>
+      </c>
+      <c r="H154" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G154,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J154" s="10" t="inlineStr">
+        <is>
+          <t>Benchmark only</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr"/>
+      <c r="L154" s="6" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>V151</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Smartwatch usage sessions</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>≈ 140</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>per day</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>307 users; about two-thirds are glances</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>S38</t>
+        </is>
+      </c>
+      <c r="H155" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G155,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>Abstract + news</t>
+        </is>
+      </c>
+      <c r="J155" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>≈ 47 touch interactions/day ≈ 3 per hour</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>140/day secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>V152</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>Smartwatch sessions shorter than 5 s; mean session</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>half; ≈ 9 s</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>S38</t>
+        </is>
+      </c>
+      <c r="H156" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G156,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>Abstract + news</t>
+        </is>
+      </c>
+      <c r="J156" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>Log-normal, median 5 s, mean 9 s</t>
+        </is>
+      </c>
+      <c r="L156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>V153</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>Smartphone uses per day; total use</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>≈ 85; ≈ 5 h</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>23 adults, 2 weeks; more than half under 30 s</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="H157" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G157,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="J157" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>5.3 per hour, median 30 s, mean 212 s</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>V154</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Face touching</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>per hour</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>26 students in a lecture</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="H158" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G158,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>Wrist self-touch not found</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>V155</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Train-interior touches per passenger movement</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>0.07 – 0.57</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>touches</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>London Underground, 16,891 passengers</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>S49</t>
+        </is>
+      </c>
+      <c r="H159" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G159,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr"/>
+      <c r="L159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>V156</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>Bengaluru Metro design loads (standing)</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>4 / 6 / 8</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>per m²</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>Normal / crush / dense crush</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="H160" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G160,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr"/>
+      <c r="L160" s="6" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>V157</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Daily life</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>One-way commute in Bengaluru</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10.84 km average</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="H161" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G161,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>Bus/metro hours per day</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>V158</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Circuit</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>OPA350 input capacitance</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>≈ 9</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>Typical</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="H162" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G162,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="J162" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>Sense-node parasitics 2.1–9 pF</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>V159</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>Circuit</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>PCB trace capacitance</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>pF/cm</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>0.8 mm trace on 0.8 mm FR-4 over a plane</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="H163" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G163,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J163" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>0.6–0.8 pF/cm × 1–3 cm</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>V160</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>Circuit</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>ESP32 SAR ADC sample-and-hold capacitance</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>≈ 1</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="H164" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G164,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr"/>
+      <c r="L164" s="6" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>V161</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>Circuit</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Parylene relative permittivity, N / C</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>2.65 / 2.95–3.15</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>1 MHz (C: 3.15 at 60 Hz)</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="H165" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G165,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="J165" s="13" t="inlineStr">
+        <is>
+          <t>In model (Oct 2026 update)</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>Coating εr 2.65–3.15</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>V162</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>Return path</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Wearable floating ground to earth</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>≤ 1</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>Wearable form factors</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="H166" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G166,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>Consistent with C_GE 0.4–2 pF</t>
+        </is>
+      </c>
+      <c r="L166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>V163</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Passive sensing</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Indoor 50 Hz electric field in homes, geometric mean</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>V/m</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>32 homes, log-normal</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>S55</t>
+        </is>
+      </c>
+      <c r="H167" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G167,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K167" s="6" t="inlineStr"/>
+      <c r="L167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>V164</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>Thermal insulation of a sari, by drape</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>0.62 – 0.94</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>clo</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>Manikin, ISO 9920</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="H168" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G168,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K168" s="6" t="inlineStr"/>
+      <c r="L168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>V165</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Harassment</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Physical harassment in public transport: touching / groping</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>58.8 / 53.2</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>% of victims</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Hyderabad, 583 respondents</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>S58</t>
+        </is>
+      </c>
+      <c r="H169" s="6">
+        <f>IFERROR(INDEX(Sources!$B:$B,MATCH(G169,Sources!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="K169" s="6" t="inlineStr"/>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L133"/>
+  <autoFilter ref="A4:L169"/>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J333" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J369" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"In model v0.3,Pending integration,Benchmark only,Context only"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7884,7 +9884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8016,7 +10016,7 @@
           <t>Ref 5</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>https://la.disneyresearch.com/wp-content/uploads/touchechi20121.pdf</t>
         </is>
@@ -8075,7 +10075,7 @@
           <t>Ref 6</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>https://la.disneyresearch.com/wp-content/uploads/capacitive-fingerprintingcameraready1.pdf</t>
         </is>
@@ -8130,7 +10130,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>https://nime.org/proceedings/2014/nime2014_515.pdf</t>
         </is>
@@ -8189,7 +10189,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>https://backend.orbit.dtu.dk/ws/files/4363898/Jonassen.pdf</t>
         </is>
@@ -8248,7 +10248,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/pdf/1805.05200.pdf</t>
         </is>
@@ -8307,7 +10307,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>https://mn.uio.no/fysikk/english/research/projects/bioimpedance/publications/papers/blemme.pdf</t>
         </is>
@@ -8362,7 +10362,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/s17030574</t>
         </is>
@@ -8417,7 +10417,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>https://par.nsf.gov/servlets/purl/10249175</t>
         </is>
@@ -8472,7 +10472,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2401.06000</t>
         </is>
@@ -8531,7 +10531,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>https://www.mdpi.com/1424-8220/22/21/8510</t>
         </is>
@@ -8590,7 +10590,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/pdf/2010.15339</t>
         </is>
@@ -8645,7 +10645,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/pdf/2003.13329</t>
         </is>
@@ -8704,7 +10704,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>https://www.thieme-connect.de/products/ejournals/pdf/10.1055/s-0039-1699403.pdf</t>
         </is>
@@ -8759,7 +10759,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>https://www.ti.com/lit/pdf/SNOA926</t>
         </is>
@@ -8820,7 +10820,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>https://hackaday.io/project/205380-adc-performance-arduino-vs-esp32-vs-ads1115</t>
         </is>
@@ -8879,7 +10879,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>https://developer.espressif.com/blog/2025/08/adc-performance/</t>
         </is>
@@ -8936,7 +10936,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>https://www.descoindustries.com/AboutESD/Voltage.aspx</t>
         </is>
@@ -8997,7 +10997,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>https://incompliancemag.com/charging-by-walking/</t>
         </is>
@@ -9052,7 +11052,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>https://dfki.de/web/forschung/projekte-publikationen/publikation/10312</t>
         </is>
@@ -9107,7 +11107,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2507.13520v1</t>
         </is>
@@ -9162,7 +11162,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>https://electrostatics.org/wp-content/uploads/2023/08/G12.pdf</t>
         </is>
@@ -9217,7 +11217,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/s16122049</t>
         </is>
@@ -9274,7 +11274,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>https://uasbangalore.edu.in/images/Agrometerology/pdf/gkvk-monthly-weather-normals-2011-2020-converted.pdf</t>
         </is>
@@ -9335,7 +11335,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>https://www.electronics.org/system/files/technical_resource/E15&amp;S22_02.pdf</t>
         </is>
@@ -9394,7 +11394,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/pdf/2501.06940</t>
         </is>
@@ -9449,7 +11449,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>https://link.springer.com/chapter/10.1007/978-981-19-0361-8_5</t>
         </is>
@@ -9504,7 +11504,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0106664</t>
         </is>
@@ -9563,7 +11563,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/pdf/2203.09669</t>
         </is>
@@ -9622,7 +11622,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>https://www.eti.uni-siegen.de/ubicomp/home/datasets/icmi18/</t>
         </is>
@@ -9677,7 +11677,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>https://arxiv.org/pdf/2608.04176</t>
         </is>
@@ -9734,7 +11734,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/10950112</t>
         </is>
@@ -9754,8 +11754,1565 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Talebzadeh et al. 2016</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>A. Talebzadeh, M. Moradian, Y. Han, D. E. Swenson, D. Pommerenke</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Effect of Human Activities and Environmental Conditions on Electrostatic Charging</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>IEEE Trans. Electromagnetic Compatibility 58(4)</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TEMC.2016.2575842</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Values from the abstract</t>
+        </is>
+      </c>
+      <c r="L35" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Kangas et al. 2015</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>M. Kangas, R. Korpelainen, I. Vikman, L. Nyberg, T. Jämsä</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Sensitivity and false alarm rate of a fall sensor in long-term fall detection in the elderly</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Gerontology 61(1):61-68</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1159/000362720</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="L36" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>S34</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Tchuente et al. 2020</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>F. Tchuente, N. Baddour, E. D. Lemaire</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Classification of Aggressive Movements Using Smartwatches</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Sensors 20(21):6377</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s20216377</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Abstract; scripted movements</t>
+        </is>
+      </c>
+      <c r="L37" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>TI OPA350 datasheet</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>OPA350, OPA2350, OPA4350 high-speed single-supply rail-to-rail operational amplifiers (SBOS099D)</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ti.com/lit/ds/symlink/opa350.pdf</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>Input capacitance, typical</t>
+        </is>
+      </c>
+      <c r="L38" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>ECN trace capacitance</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ECN / passive-components.eu (using TI figures)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>A Plague of Parasites (PCB trace capacitance)</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Trade article</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Trade article</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>https://passive-components.eu/</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>0.8 mm trace on 0.8 mm FR-4 over a plane</t>
+        </is>
+      </c>
+      <c r="L39" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>SCS parylene data</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Specialty Coating Systems</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Parylene Dielectric Properties</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturer technical data</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturer data</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>https://scscoatings.com/</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>Parylene N and C relative permittivity</t>
+        </is>
+      </c>
+      <c r="L40" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>S38</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Visuri et al. 2017</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>A. Visuri, Z. Sarsenbayeva, N. van Berkel, J. Goncalves, R. Rawassizadeh, V. Kostakos, D. Ferreira</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Quantifying Sources and Types of Smartwatch Usage Sessions</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Proc. ACM CHI 2017, pp. 3569-3581</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Peer-reviewed conference</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3025453.3025817</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>'Half of sessions under 5 s' in the abstract; 140 sessions/day and ~9 s mean via University of Oulu news</t>
+        </is>
+      </c>
+      <c r="L41" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Andrews et al. 2015</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>S. Andrews, D. A. Ellis, H. Shaw, L. Piwek</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Beyond Self-Report: Tools to Compare Estimated and Real-World Smartphone Use</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>PLoS ONE 10(10):e0139004</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0139004</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>85 uses/day and ~5 h/day via Lancaster University press release</t>
+        </is>
+      </c>
+      <c r="L42" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Ficker 2005</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>T. Ficker</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Charging by walking</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>J. Phys. D: Appl. Phys. 38(5):410-417</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>Numbers seen in In Compliance Magazine's summary of Ficker's work (secondary); check the paper</t>
+        </is>
+      </c>
+      <c r="L43" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Tudor-Locke et al. 2012</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C. Tudor-Locke, H. Han, E. J. Aguiar, et al.</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Using cadence to study free-living ambulatory activity</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Sports Medicine 42(5):381-398</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Journal article (review)</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>https://strathprints.strath.ac.uk/42646/</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Neacsu et al. 2007</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>D. Neacsu, A. Salceanu, E. Lunca, V. David</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Indirect Measurements on the Capacity in the Electrostatic HB Model</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>IMEKO TC4 Symposium, Iasi</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>2007</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Conference paper</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>https://imeko.org/proceedings/indirect-measurements-on-the-capacity-in-the-electrostatic-hb-model</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Abstract/snippet</t>
+        </is>
+      </c>
+      <c r="L45" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>S43</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Dawkins et al. 2022</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>N. P. Dawkins, T. Yates, et al.</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Normative wrist-worn accelerometer values for self-paced walking and running: a walk in the park</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>J. Sports Sciences</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/02640414.2021.1976491</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Averaged ENMO values, not peaks</t>
+        </is>
+      </c>
+      <c r="L46" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Walking recognition 2022</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>(authors as listed on arXiv)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>A 'one-size-fits-most' walking recognition method for smartphones, smartwatches, and wearable accelerometers</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>arXiv:2207.07443</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2207.07443</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr"/>
+      <c r="L47" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Public transport perturbation 2020</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>(authors not visible in the abstract)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Perturbation in public transport as a basic concept for perturbation-based balance training for fall prevention</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Z. Gerontol. Geriatr.</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/journal/391</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>12 days of bus and tram recordings, sensor on a vertical bar</t>
+        </is>
+      </c>
+      <c r="L48" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>S46</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Perry &amp; Burnfield 2010</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>J. Perry, J. M. Burnfield</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Gait Analysis: Normal and Pathological Function, 2nd ed.</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>SLACK Inc.</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Textbook</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>https://www.healio.com/books</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Standard gait-phase percentages</t>
+        </is>
+      </c>
+      <c r="L49" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>S47</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Krašna et al. 2021</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>S. Krašna, et al.</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Human Response to Longitudinal Perturbations of Standing Passengers on Public Transport During Regular Operation</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Frontiers in Bioengineering and Biotechnology 9:680883</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3389/fbioe.2021.680883</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Kwok et al. 2015</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Y. L. A. Kwok, J. Gralton, M.-L. McLaws</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Face touching: a frequent habit that has implications for hand hygiene</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>American Journal of Infection Control 43(2):112-114</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.ajic.2014.10.015</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr"/>
+      <c r="L51" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>S49</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Mow et al. 2024</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>S. Mow, S. Seriani, T. Fujiyama</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Where and how often do people touch train interiors? An investigation during the pandemic</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Proc. ICE Municipal Engineer</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>https://discovery.ucl.ac.uk/id/eprint/10199779/</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr"/>
+      <c r="L52" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>BMRCL EIA</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Bangalore Metro Rail Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Impact Assessment (design passenger loads)</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>BMRCL / JICA</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jica.go.jp/</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>ISEC WP 437 (2019)</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Institute for Social and Economic Change</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Determinants of intra-urban mobility: a study of Bengaluru (Working Paper 437)</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ISEC</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Working paper</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/p/sch/wpaper/437.html</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr"/>
+      <c r="L54" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Espressif ESP-FAQ</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Espressif Systems</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>ESP-FAQ: ADC</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Espressif documentation</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturer documentation</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>https://docs.espressif.com/projects/esp-faq/</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Step-to-Charge 2024</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>(Sen group, Purdue)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Step-to-Charge (EQS body powering)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>arXiv:2408.01927</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.01927</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>S54</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>IEC 61000-4-2</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>IEC</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>IEC 61000-4-2: Electrostatic discharge immunity test</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>International standard</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>https://webstore.iec.ch/publication/4189</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>Human-body model and current waveform</t>
+        </is>
+      </c>
+      <c r="L57" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>S55</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Ramallah ELF survey</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>(Al-Quds / An-Najah University)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Residential exposure to ELF electric and magnetic fields in the city of Ramallah-Palestine</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>https://dspace.alquds.edu/items/bc4377ca-bfb7-4375-ab1a-435c8e020c57/full</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>S56</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Aziz et al. 2017</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>O. Aziz, et al.</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Validation of accuracy of SVM-based fall detection system using real-world fall and non-fall datasets</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>PLoS ONE 12(7):e0180318</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0180318</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Indraganti et al. 2014</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>M. Indraganti, et al.</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Thermal insulation of Indian clothing ensembles (sari, salwar-kurti)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Windsor Conference</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Conference paper</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>https://architexturez.net/node/175314</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>S58</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Majumdar et al. (Hyderabad)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>B. B. Majumdar, et al. (BITS Pilani Hyderabad)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Harassment of women in public transport, Hyderabad</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Transportation Research Record</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/home/trr</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Numbers via press coverage (secondary)</t>
+        </is>
+      </c>
+      <c r="L61" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A61)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:L34"/>
+  <autoFilter ref="A3:L61"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
@@ -9788,6 +13345,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9974,7 +13558,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>100 ±5% + 2–7</t>
+          <t>100 ±5% + 2.1–9 + (0.6–0.8 pF/cm × 1–3 cm)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -9982,19 +13566,19 @@
           <t>pF</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>S/E</t>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>S/D</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>S3, S8</t>
+          <t>S3, S8, S35, S36</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Parasitics part estimated</t>
+          <t>Trace length is a design choice</t>
         </is>
       </c>
     </row>
@@ -10056,7 +13640,7 @@
           <t>cm²</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -10464,27 +14048,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>±5</t>
+          <t>160 → 100 pF (σ 0.235)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>S/E</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>S4, S9</t>
+          <t>S4, S40</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Direction sourced, size estimated</t>
+          <t>Sweep insensitive (≤ 0.002 % FS)</t>
         </is>
       </c>
     </row>
@@ -10744,7 +14328,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>25–100 µm, εr 3</t>
+          <t>25–100 µm, εr 2.65–3.15</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -10752,19 +14336,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>D/S</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Design choice</t>
+          <t>Thickness is a design choice; parylene εr</t>
         </is>
       </c>
     </row>

--- a/docs/SparshaGuard_parameter_sources.xlsx
+++ b/docs/SparshaGuard_parameter_sources.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Values from Papers'!$A$4:$L$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sources'!$A$3:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sources'!$A$3:$L$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Model v0.3 Params'!$A$3:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9884,7 +9884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13311,8 +13311,128 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Nabors &amp; White 1991 (FastCap)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>K. Nabors, J. White</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>FastCap: A Multipole Accelerated 3-D Capacitance Extraction Program</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>IEEE Trans. Computer-Aided Design 10(11):1447-1459</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>1991</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Journal article</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/43.97624</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Reference solver used to check the 3D field calculation</t>
+        </is>
+      </c>
+      <c r="L62" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>ngspice manual</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>H. Vogt, G. Atkinson, P. Nenzi</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Ngspice User's Manual</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>ngspice project</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>https://ngspice.sourceforge.io/docs.html</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Circuit simulator used to check the Python solver</t>
+        </is>
+      </c>
+      <c r="L63" s="6">
+        <f>COUNTIF('Values from Papers'!$G:$G,A63)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:L61"/>
+  <autoFilter ref="A3:L63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
@@ -13372,6 +13492,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
